--- a/cet4/result/30_医道女神_白衣天使的传奇/30_医道女神_白衣天使的传奇_学习版.xlsx
+++ b/cet4/result/30_医道女神_白衣天使的传奇/30_医道女神_白衣天使的传奇_学习版.xlsx
@@ -397,857 +397,647 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D45"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>sleepy</v>
       </c>
       <c r="B2" t="str">
-        <v>sleepy</v>
+        <v>/ˈsliːpi/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>困倦的</v>
       </c>
-      <c r="D2" t="str">
-        <v>sleepy(困倦的)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>new</v>
       </c>
       <c r="B3" t="str">
-        <v>new</v>
+        <v>/nuː/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D3" t="str">
         <v>新</v>
       </c>
-      <c r="D3" t="str">
-        <v>new(新)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>button</v>
       </c>
       <c r="B4" t="str">
-        <v>button</v>
+        <v>/ˈbʌtn/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D4" t="str">
         <v>按钮</v>
       </c>
-      <c r="D4" t="str">
-        <v>button(按钮)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>holy</v>
       </c>
       <c r="B5" t="str">
-        <v>holy</v>
+        <v>/ˈhoʊli/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>神圣的</v>
       </c>
-      <c r="D5" t="str">
-        <v>holy(神圣的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>emergency</v>
       </c>
       <c r="B6" t="str">
-        <v>emergency</v>
+        <v>/ɪˈmɜːrdʒənsi/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>紧急情况</v>
       </c>
-      <c r="D6" t="str">
-        <v>emergency(紧急情况)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>question</v>
       </c>
       <c r="B7" t="str">
-        <v>question</v>
+        <v>/ˈkwestʃən/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>问题</v>
       </c>
-      <c r="D7" t="str">
-        <v>question(问题)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>handwriting</v>
       </c>
       <c r="B8" t="str">
-        <v>handwriting</v>
+        <v>/ˈhændraɪtɪŋ/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>笔迹</v>
       </c>
-      <c r="D8" t="str">
-        <v>handwriting(笔迹)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>breathe</v>
       </c>
       <c r="B9" t="str">
-        <v>breathe</v>
+        <v>/briːð/</v>
       </c>
       <c r="C9" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>呼吸</v>
       </c>
-      <c r="D9" t="str">
-        <v>breathe(呼吸)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>family</v>
       </c>
       <c r="B10" t="str">
-        <v>family</v>
+        <v>/ˈfæməli/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>家庭</v>
       </c>
-      <c r="D10" t="str">
-        <v>family(家庭)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>receive</v>
       </c>
       <c r="B11" t="str">
-        <v>receive</v>
+        <v>/rɪˈsiːv/</v>
       </c>
       <c r="C11" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>接收</v>
       </c>
-      <c r="D11" t="str">
-        <v>receive(接收)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>support</v>
       </c>
       <c r="B12" t="str">
-        <v>support</v>
+        <v>/səˈpɔːrt/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D12" t="str">
         <v>支持</v>
       </c>
-      <c r="D12" t="str">
-        <v>support(支持)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>shriek</v>
       </c>
       <c r="B13" t="str">
-        <v>shriek</v>
+        <v>/ʃriːk/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D13" t="str">
         <v>尖叫</v>
       </c>
-      <c r="D13" t="str">
-        <v>shriek(尖叫)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>burn</v>
       </c>
       <c r="B14" t="str">
-        <v>burn</v>
+        <v>/bɜːrn/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D14" t="str">
         <v>灼伤</v>
       </c>
-      <c r="D14" t="str">
-        <v>burn(灼伤)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>complain</v>
       </c>
       <c r="B15" t="str">
-        <v>complain</v>
+        <v>/kəmˈpleɪn/</v>
       </c>
       <c r="C15" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>抱怨</v>
       </c>
-      <c r="D15" t="str">
-        <v>complain(抱怨)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>every</v>
       </c>
       <c r="B16" t="str">
-        <v>every</v>
+        <v>/ˈevri/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>每一个</v>
       </c>
-      <c r="D16" t="str">
-        <v>every(每一个)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>portion</v>
       </c>
       <c r="B17" t="str">
-        <v>portion</v>
+        <v>/ˈpɔːrʃn/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D17" t="str">
         <v>部分</v>
       </c>
-      <c r="D17" t="str">
-        <v>portion(部分)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>beef</v>
       </c>
       <c r="B18" t="str">
-        <v>beef</v>
+        <v>/biːf/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>牛肉</v>
       </c>
-      <c r="D18" t="str">
-        <v>beef(牛肉)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>journal</v>
       </c>
       <c r="B19" t="str">
-        <v>journal</v>
+        <v>/ˈdʒɜːrnl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>期刊</v>
       </c>
-      <c r="D19" t="str">
-        <v>journal(期刊)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>discover</v>
       </c>
       <c r="B20" t="str">
-        <v>discover</v>
+        <v>/dɪˈskʌvər/</v>
       </c>
       <c r="C20" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>发现</v>
       </c>
-      <c r="D20" t="str">
-        <v>discover(发现)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>four</v>
       </c>
       <c r="B21" t="str">
-        <v>four</v>
+        <v>/fɔːr/</v>
       </c>
       <c r="C21" t="str">
+        <v>num.</v>
+      </c>
+      <c r="D21" t="str">
         <v>四</v>
       </c>
-      <c r="D21" t="str">
-        <v>four(四)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>experience</v>
       </c>
       <c r="B22" t="str">
-        <v>experience</v>
+        <v>/ɪkˈspɪriəns/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D22" t="str">
         <v>经验</v>
       </c>
-      <c r="D22" t="str">
-        <v>experience(经验)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>arise</v>
       </c>
       <c r="B23" t="str">
-        <v>arise</v>
+        <v>/əˈraɪz/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>出现</v>
       </c>
-      <c r="D23" t="str">
-        <v>arise(出现)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>suppose</v>
       </c>
       <c r="B24" t="str">
-        <v>family</v>
+        <v>/səˈpoʊz/</v>
       </c>
       <c r="C24" t="str">
-        <v>家庭</v>
+        <v>vt./vi./conj.</v>
       </c>
       <c r="D24" t="str">
-        <v>family(家庭)📢</v>
+        <v>假设</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>tight</v>
       </c>
       <c r="B25" t="str">
-        <v>suppose</v>
+        <v>/taɪt/</v>
       </c>
       <c r="C25" t="str">
-        <v>假设</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D25" t="str">
-        <v>suppose(假设)📢</v>
+        <v>紧张的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>guidance</v>
       </c>
       <c r="B26" t="str">
-        <v>tight</v>
+        <v>/ˈɡaɪdns/</v>
       </c>
       <c r="C26" t="str">
-        <v>紧张的</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>tight(紧张的)📢</v>
+        <v>指导</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>behavior</v>
       </c>
       <c r="B27" t="str">
-        <v>guidance</v>
+        <v>/bɪˈheɪvjər/</v>
       </c>
       <c r="C27" t="str">
-        <v>指导</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>guidance(指导)📢</v>
+        <v>行为</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>librarian</v>
       </c>
       <c r="B28" t="str">
-        <v>behavior</v>
+        <v>/laɪˈbreriən/</v>
       </c>
       <c r="C28" t="str">
-        <v>行为</v>
+        <v>n.</v>
       </c>
       <c r="D28" t="str">
-        <v>behavior(行为)📢</v>
+        <v>图书馆</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>important</v>
       </c>
       <c r="B29" t="str">
-        <v>librarian</v>
+        <v>/ɪmˈpɔːrtnt/</v>
       </c>
       <c r="C29" t="str">
-        <v>图书馆</v>
+        <v>adj.</v>
       </c>
       <c r="D29" t="str">
-        <v>librarian(图书馆)📢</v>
+        <v>重要的</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>collective</v>
       </c>
       <c r="B30" t="str">
-        <v>important</v>
+        <v>/kəˈlektɪv/</v>
       </c>
       <c r="C30" t="str">
-        <v>重要的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>important(重要的)📢</v>
+        <v>集体的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>figure</v>
       </c>
       <c r="B31" t="str">
-        <v>collective</v>
+        <v>/ˈfɪɡjər/</v>
       </c>
       <c r="C31" t="str">
-        <v>集体的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>collective(集体的)📢</v>
+        <v>人物</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>scholar</v>
       </c>
       <c r="B32" t="str">
-        <v>figure</v>
+        <v>/ˈskɑːlər/</v>
       </c>
       <c r="C32" t="str">
-        <v>人物</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>figure(人物)📢</v>
+        <v>学者</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>praise</v>
       </c>
       <c r="B33" t="str">
-        <v>new</v>
+        <v>/preɪz/</v>
       </c>
       <c r="C33" t="str">
-        <v>新</v>
+        <v>n./v.</v>
       </c>
       <c r="D33" t="str">
-        <v>new(新)📢</v>
+        <v>赞扬</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>cruel</v>
       </c>
       <c r="B34" t="str">
-        <v>scholar</v>
+        <v>/ˈkruːəl/</v>
       </c>
       <c r="C34" t="str">
-        <v>学者</v>
+        <v>adj.</v>
       </c>
       <c r="D34" t="str">
-        <v>scholar(学者)📢</v>
+        <v>残酷的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>error</v>
       </c>
       <c r="B35" t="str">
-        <v>praise</v>
+        <v>/ˈerər/</v>
       </c>
       <c r="C35" t="str">
-        <v>赞扬</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>praise(赞扬)📢</v>
+        <v>错误</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>cheque</v>
       </c>
       <c r="B36" t="str">
-        <v>experience</v>
+        <v>/tʃek/</v>
       </c>
       <c r="C36" t="str">
-        <v>经验</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>experience(经验)📢</v>
+        <v>支票</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>widespread</v>
       </c>
       <c r="B37" t="str">
-        <v>emergency</v>
+        <v>/ˈwaɪdspred/</v>
       </c>
       <c r="C37" t="str">
-        <v>紧急情况</v>
+        <v>adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>emergency(紧急情况)📢</v>
+        <v>广泛的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>prove</v>
       </c>
       <c r="B38" t="str">
-        <v>cruel</v>
+        <v>/pruːv/</v>
       </c>
       <c r="C38" t="str">
-        <v>残酷的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>cruel(残酷的)📢</v>
+        <v>证明</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>nod</v>
       </c>
       <c r="B39" t="str">
-        <v>family</v>
+        <v>/nɑːd/</v>
       </c>
       <c r="C39" t="str">
-        <v>家庭</v>
+        <v>n./v.</v>
       </c>
       <c r="D39" t="str">
-        <v>family(家庭)📢</v>
+        <v>点头</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>stamp</v>
       </c>
       <c r="B40" t="str">
-        <v>new</v>
+        <v>/stæmp/</v>
       </c>
       <c r="C40" t="str">
-        <v>新</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>new(新)📢</v>
+        <v>邮票</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>foreigner</v>
       </c>
       <c r="B41" t="str">
-        <v>collective</v>
+        <v>/ˈfɔːrənər/</v>
       </c>
       <c r="C41" t="str">
-        <v>集体的</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>collective(集体的)📢</v>
+        <v>外国人</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>fluent</v>
       </c>
       <c r="B42" t="str">
-        <v>four</v>
+        <v>/ˈfluːənt/</v>
       </c>
       <c r="C42" t="str">
-        <v>四</v>
+        <v>adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>four(四)📢</v>
+        <v>流利的</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>cassette</v>
       </c>
       <c r="B43" t="str">
-        <v>tight</v>
+        <v>/kəˈset/</v>
       </c>
       <c r="C43" t="str">
-        <v>紧迫的</v>
+        <v>n.</v>
       </c>
       <c r="D43" t="str">
-        <v>tight(紧迫的)📢</v>
+        <v>卡带</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>truth</v>
       </c>
       <c r="B44" t="str">
-        <v>error</v>
+        <v>/truːθ/</v>
       </c>
       <c r="C44" t="str">
-        <v>错误</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>error(错误)📢</v>
+        <v>真理</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>damp</v>
       </c>
       <c r="B45" t="str">
-        <v>cheque</v>
+        <v>/dæmp/</v>
       </c>
       <c r="C45" t="str">
-        <v>支票</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D45" t="str">
-        <v>cheque(支票)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>receive</v>
-      </c>
-      <c r="C46" t="str">
-        <v>接收</v>
-      </c>
-      <c r="D46" t="str">
-        <v>receive(接收)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>widespread</v>
-      </c>
-      <c r="C47" t="str">
-        <v>广泛的</v>
-      </c>
-      <c r="D47" t="str">
-        <v>widespread(广泛的)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>prove</v>
-      </c>
-      <c r="C48" t="str">
-        <v>证明</v>
-      </c>
-      <c r="D48" t="str">
-        <v>prove(证明)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>nod</v>
-      </c>
-      <c r="C49" t="str">
-        <v>点头</v>
-      </c>
-      <c r="D49" t="str">
-        <v>nod(点头)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>stamp</v>
-      </c>
-      <c r="C50" t="str">
-        <v>邮票</v>
-      </c>
-      <c r="D50" t="str">
-        <v>stamp(邮票)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>praise</v>
-      </c>
-      <c r="C51" t="str">
-        <v>赞扬</v>
-      </c>
-      <c r="D51" t="str">
-        <v>praise(赞扬)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>new</v>
-      </c>
-      <c r="C52" t="str">
-        <v>新</v>
-      </c>
-      <c r="D52" t="str">
-        <v>new(新)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>holy</v>
-      </c>
-      <c r="C53" t="str">
-        <v>神圣的</v>
-      </c>
-      <c r="D53" t="str">
-        <v>holy(神圣的)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>nod</v>
-      </c>
-      <c r="C54" t="str">
-        <v>点头</v>
-      </c>
-      <c r="D54" t="str">
-        <v>nod(点头)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>foreigner</v>
-      </c>
-      <c r="C55" t="str">
-        <v>外国人</v>
-      </c>
-      <c r="D55" t="str">
-        <v>foreigner(外国人)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>fluent</v>
-      </c>
-      <c r="C56" t="str">
-        <v>流利的</v>
-      </c>
-      <c r="D56" t="str">
-        <v>fluent(流利的)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>cassette</v>
-      </c>
-      <c r="C57" t="str">
-        <v>卡带</v>
-      </c>
-      <c r="D57" t="str">
-        <v>cassette(卡带)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>four</v>
-      </c>
-      <c r="C58" t="str">
-        <v>四</v>
-      </c>
-      <c r="D58" t="str">
-        <v>four(四)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>truth</v>
-      </c>
-      <c r="C59" t="str">
-        <v>真理</v>
-      </c>
-      <c r="D59" t="str">
-        <v>truth(真理)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>damp</v>
-      </c>
-      <c r="C60" t="str">
         <v>潮湿的</v>
-      </c>
-      <c r="D60" t="str">
-        <v>damp(潮湿的)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>